--- a/src/main/resources/benchmarks.xlsx
+++ b/src/main/resources/benchmarks.xlsx
@@ -3,13 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="164011"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\n_alv\artevolver2019\src\main\resources\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17730" firstSheet="4" activeTab="8"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="32310" windowHeight="11805" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -23,6 +18,7 @@
     <sheet name="ArtEvolver2019 Stats #2" sheetId="7" r:id="rId9"/>
   </sheets>
   <calcPr calcId="162913"/>
+  <oleSize ref="A13:AE49"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -977,6 +973,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1002,7 +999,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="es-AR"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -1290,7 +1287,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-AR"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="445999296"/>
@@ -1349,7 +1346,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-AR"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="445998880"/>
@@ -1390,7 +1387,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="es-AR"/>
+      <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -1467,7 +1464,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="es-AR"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -37077,7 +37074,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-AR"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="478271936"/>
@@ -37141,7 +37138,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-AR"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="478271608"/>
@@ -37182,7 +37179,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="es-AR"/>
+      <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
